--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.06427920124112</v>
+        <v>11.54794537020168</v>
       </c>
       <c r="D2" t="n">
-        <v>70.23370886951616</v>
+        <v>11.41297769129638</v>
       </c>
       <c r="E2" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F2" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.29497090571037</v>
+        <v>9.797932772177935</v>
       </c>
       <c r="D3" t="n">
-        <v>59.45596118269081</v>
+        <v>9.661593692187257</v>
       </c>
       <c r="E3" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F3" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66814099979952</v>
+        <v>6.933572912467422</v>
       </c>
       <c r="D4" t="n">
-        <v>42.57564226435622</v>
+        <v>6.918541867957885</v>
       </c>
       <c r="E4" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F4" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.67688091843976</v>
+        <v>8.234993149246462</v>
       </c>
       <c r="D5" t="n">
-        <v>50.85610989893038</v>
+        <v>8.264117858576187</v>
       </c>
       <c r="E5" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F5" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>61.21639472172663</v>
+        <v>9.947664142280578</v>
       </c>
       <c r="D6" t="n">
-        <v>61.62858834054693</v>
+        <v>10.01464560533888</v>
       </c>
       <c r="E6" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F6" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.61388019044352</v>
+        <v>5.787255530947073</v>
       </c>
       <c r="D7" t="n">
-        <v>36.40742496955245</v>
+        <v>5.916206557552274</v>
       </c>
       <c r="E7" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F7" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.32813256125657</v>
+        <v>6.228321541204194</v>
       </c>
       <c r="D8" t="n">
-        <v>38.54051655203365</v>
+        <v>6.262833939705469</v>
       </c>
       <c r="E8" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F8" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.35110469262929</v>
+        <v>9.807054512552261</v>
       </c>
       <c r="D9" t="n">
-        <v>61.04306253191142</v>
+        <v>9.919497661435605</v>
       </c>
       <c r="E9" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F9" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.76365586096448</v>
+        <v>2.724094077406728</v>
       </c>
       <c r="D10" t="n">
-        <v>16.51842758549007</v>
+        <v>2.684244482642137</v>
       </c>
       <c r="E10" t="n">
-        <v>15.86702375020343</v>
+        <v>2.578391359408057</v>
       </c>
       <c r="F10" t="n">
-        <v>15.74414627200568</v>
+        <v>2.558423769200922</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
